--- a/NBFC-MF/Borrowers/Tina_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Tina_Daily.xlsx
@@ -902,31 +902,33 @@
       <c r="K5" s="26"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A6" s="2">
+        <v>46295</v>
+      </c>
+      <c r="B6" s="23">
+        <f t="shared" si="3"/>
+        <v>5</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="4" t="str">
+      <c r="D6" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E6" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E6" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F6" s="4" t="str">
+        <v>30.280056751114994</v>
+      </c>
+      <c r="F6" s="4">
         <f>IF(AND($A6&lt;&gt;"",$B6&lt;&gt;""),D6-E6,"")</f>
-        <v/>
-      </c>
-      <c r="G6" s="4" t="str">
+        <v>69.719943248885002</v>
+      </c>
+      <c r="G6" s="4">
         <f t="shared" ref="G6:G69" si="4">IF(AND($A6&lt;&gt;"",$B6&lt;&gt;""),G5-F6,"")</f>
-        <v/>
-      </c>
-      <c r="H6" s="4" t="str">
+        <v>9653.5580399133705</v>
+      </c>
+      <c r="H6" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>346.44196008662948</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>13</v>
@@ -934,31 +936,33 @@
       <c r="K6" s="26"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="19"/>
-      <c r="B7" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A7" s="19">
+        <v>46296</v>
+      </c>
+      <c r="B7" s="24">
+        <f t="shared" si="3"/>
+        <v>6</v>
       </c>
       <c r="C7" s="20"/>
-      <c r="D7" s="21" t="str">
+      <c r="D7" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E7" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E7" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F7" s="21" t="str">
+        <v>30.062936162573088</v>
+      </c>
+      <c r="F7" s="21">
         <f t="shared" ref="F7:F70" si="5">IF(AND($A7&lt;&gt;"",$B7&lt;&gt;""),D7-E7,"")</f>
-        <v/>
-      </c>
-      <c r="G7" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H7" s="21" t="str">
+        <v>69.937063837426905</v>
+      </c>
+      <c r="G7" s="21">
+        <f t="shared" si="4"/>
+        <v>9583.620976075943</v>
+      </c>
+      <c r="H7" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>416.37902392405704</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>7</v>
@@ -968,31 +972,33 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A8" s="2">
+        <v>46297</v>
+      </c>
+      <c r="B8" s="23">
+        <f t="shared" si="3"/>
+        <v>7</v>
       </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="4" t="str">
+      <c r="D8" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E8" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E8" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F8" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G8" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H8" s="4" t="str">
+        <v>29.845139421014235</v>
+      </c>
+      <c r="F8" s="4">
+        <f t="shared" si="5"/>
+        <v>70.154860578985762</v>
+      </c>
+      <c r="G8" s="4">
+        <f t="shared" si="4"/>
+        <v>9513.4661154969581</v>
+      </c>
+      <c r="H8" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>486.53388450304192</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>14</v>
@@ -1003,31 +1009,33 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="19"/>
-      <c r="B9" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A9" s="19">
+        <v>46298</v>
+      </c>
+      <c r="B9" s="24">
+        <f t="shared" si="3"/>
+        <v>8</v>
       </c>
       <c r="C9" s="20"/>
-      <c r="D9" s="21" t="str">
+      <c r="D9" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E9" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E9" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F9" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G9" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H9" s="21" t="str">
+        <v>29.626664420774929</v>
+      </c>
+      <c r="F9" s="21">
+        <f t="shared" si="5"/>
+        <v>70.373335579225071</v>
+      </c>
+      <c r="G9" s="21">
+        <f t="shared" si="4"/>
+        <v>9443.0927799177334</v>
+      </c>
+      <c r="H9" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>556.90722008226658</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>8</v>
@@ -1037,31 +1045,33 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A10" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B10" s="23">
+        <f t="shared" si="3"/>
+        <v>9</v>
       </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="4" t="str">
+      <c r="D10" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E10" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E10" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F10" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G10" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H10" s="4" t="str">
+        <v>29.407509049634221</v>
+      </c>
+      <c r="F10" s="4">
+        <f t="shared" si="5"/>
+        <v>70.592490950365772</v>
+      </c>
+      <c r="G10" s="4">
+        <f t="shared" si="4"/>
+        <v>9372.5002889673669</v>
+      </c>
+      <c r="H10" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>627.49971103263306</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>15</v>
@@ -1071,201 +1081,213 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="19"/>
-      <c r="B11" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A11" s="19">
+        <v>46300</v>
+      </c>
+      <c r="B11" s="24">
+        <f t="shared" si="3"/>
+        <v>10</v>
       </c>
       <c r="C11" s="20"/>
-      <c r="D11" s="21" t="str">
+      <c r="D11" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E11" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E11" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F11" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G11" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H11" s="21" t="str">
+        <v>29.187671188793338</v>
+      </c>
+      <c r="F11" s="21">
+        <f t="shared" si="5"/>
+        <v>70.812328811206669</v>
+      </c>
+      <c r="G11" s="21">
+        <f t="shared" si="4"/>
+        <v>9301.6879601561595</v>
+      </c>
+      <c r="H11" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>698.31203984384047</v>
       </c>
       <c r="J11" s="8"/>
       <c r="L11" s="22"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A12" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B12" s="23">
+        <f t="shared" si="3"/>
+        <v>11</v>
       </c>
       <c r="C12" s="3"/>
-      <c r="D12" s="4" t="str">
+      <c r="D12" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E12" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E12" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F12" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G12" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H12" s="4" t="str">
+        <v>28.967148712855174</v>
+      </c>
+      <c r="F12" s="4">
+        <f t="shared" si="5"/>
+        <v>71.032851287144823</v>
+      </c>
+      <c r="G12" s="4">
+        <f t="shared" si="4"/>
+        <v>9230.6551088690139</v>
+      </c>
+      <c r="H12" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>769.34489113098607</v>
       </c>
       <c r="J12" s="9" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="19"/>
-      <c r="B13" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A13" s="19">
+        <v>46302</v>
+      </c>
+      <c r="B13" s="24">
+        <f t="shared" si="3"/>
+        <v>12</v>
       </c>
       <c r="C13" s="20"/>
-      <c r="D13" s="21" t="str">
+      <c r="D13" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E13" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E13" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F13" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G13" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H13" s="21" t="str">
+        <v>28.745939489803757</v>
+      </c>
+      <c r="F13" s="21">
+        <f t="shared" si="5"/>
+        <v>71.25406051019624</v>
+      </c>
+      <c r="G13" s="21">
+        <f t="shared" si="4"/>
+        <v>9159.4010483588172</v>
+      </c>
+      <c r="H13" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>840.59895164118279</v>
       </c>
       <c r="J13" s="25" t="s">
         <v>21</v>
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>11600</v>
+        <v>10300</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A14" s="2">
+        <v>46303</v>
+      </c>
+      <c r="B14" s="23">
+        <f t="shared" si="3"/>
+        <v>13</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="4" t="str">
+      <c r="D14" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E14" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E14" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F14" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G14" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H14" s="4" t="str">
+        <v>28.524041380983622</v>
+      </c>
+      <c r="F14" s="4">
+        <f t="shared" si="5"/>
+        <v>71.475958619016382</v>
+      </c>
+      <c r="G14" s="4">
+        <f t="shared" si="4"/>
+        <v>9087.9250897398015</v>
+      </c>
+      <c r="H14" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>912.07491026019852</v>
       </c>
       <c r="J14" s="11" t="s">
         <v>22</v>
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>9723.2779831622556</v>
+        <v>8799.7884212336685</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="19"/>
-      <c r="B15" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A15" s="19">
+        <v>46304</v>
+      </c>
+      <c r="B15" s="24">
+        <f t="shared" si="3"/>
+        <v>14</v>
       </c>
       <c r="C15" s="20"/>
-      <c r="D15" s="21" t="str">
+      <c r="D15" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E15" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E15" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F15" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G15" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H15" s="21" t="str">
+        <v>28.301452241079154</v>
+      </c>
+      <c r="F15" s="21">
+        <f t="shared" si="5"/>
+        <v>71.698547758920853</v>
+      </c>
+      <c r="G15" s="21">
+        <f t="shared" si="4"/>
+        <v>9016.2265419808809</v>
+      </c>
+      <c r="H15" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>983.77345801911906</v>
       </c>
       <c r="J15" s="13" t="s">
         <v>6</v>
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>276.72201683774438</v>
+        <v>1200.2115787663315</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A16" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B16" s="23">
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="C16" s="3"/>
-      <c r="D16" s="4" t="str">
+      <c r="D16" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E16" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E16" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F16" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G16" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H16" s="4" t="str">
+        <v>28.078169918093817</v>
+      </c>
+      <c r="F16" s="4">
+        <f t="shared" si="5"/>
+        <v>71.92183008190618</v>
+      </c>
+      <c r="G16" s="4">
+        <f t="shared" si="4"/>
+        <v>8944.3047118989743</v>
+      </c>
+      <c r="H16" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1055.6952881010257</v>
       </c>
       <c r="J16" s="15" t="s">
         <v>18</v>
@@ -1276,31 +1298,33 @@
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="19"/>
-      <c r="B17" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A17" s="19">
+        <v>46306</v>
+      </c>
+      <c r="B17" s="24">
+        <f t="shared" si="3"/>
+        <v>16</v>
       </c>
       <c r="C17" s="20"/>
-      <c r="D17" s="21" t="str">
+      <c r="D17" s="21">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E17" s="21" t="str">
+        <v>100</v>
+      </c>
+      <c r="E17" s="21">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F17" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G17" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H17" s="21" t="str">
+        <v>27.854192253329376</v>
+      </c>
+      <c r="F17" s="21">
+        <f t="shared" si="5"/>
+        <v>72.145807746670627</v>
+      </c>
+      <c r="G17" s="21">
+        <f t="shared" si="4"/>
+        <v>8872.1589041523039</v>
+      </c>
+      <c r="H17" s="21">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1127.8410958476961</v>
       </c>
       <c r="J17" s="17" t="s">
         <v>19</v>
@@ -1311,31 +1335,33 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A18" s="2">
+        <v>46307</v>
+      </c>
+      <c r="B18" s="23">
+        <f t="shared" si="3"/>
+        <v>17</v>
       </c>
       <c r="C18" s="3"/>
-      <c r="D18" s="4" t="str">
+      <c r="D18" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E18" s="4" t="str">
+        <v>100</v>
+      </c>
+      <c r="E18" s="4">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F18" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G18" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H18" s="4" t="str">
+        <v>27.629517081365023</v>
+      </c>
+      <c r="F18" s="4">
+        <f t="shared" si="5"/>
+        <v>72.370482918634977</v>
+      </c>
+      <c r="G18" s="4">
+        <f t="shared" si="4"/>
+        <v>8799.7884212336685</v>
+      </c>
+      <c r="H18" s="4">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1200.2115787663315</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
